--- a/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
+++ b/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
@@ -779,7 +779,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <v>46306.65612717593</v>
+        <v>46306.92436550926</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -787,7 +787,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -809,13 +809,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7">
-        <v>12759.339999999997</v>
+        <v>12759.34</v>
       </c>
       <c r="C17" s="7">
-        <v>12785.670000000004</v>
+        <v>12785.669999999996</v>
       </c>
       <c r="D17" s="8">
-        <v>-0.002059336741837322</v>
+        <v>-0.0020593367418364696</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -865,13 +865,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>6.6351222048881935</v>
+        <v>6.635122204888195</v>
       </c>
       <c r="C21" s="7">
-        <v>6.739942013705853</v>
+        <v>6.73994201370585</v>
       </c>
       <c r="D21" s="8">
-        <v>-0.015552034216986744</v>
+        <v>-0.01555203421698596</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>0.7570511451287526</v>
+        <v>0.7570511451287528</v>
       </c>
       <c r="C23" s="7">
-        <v>0.7465212821860223</v>
+        <v>0.7465212821860219</v>
       </c>
       <c r="D23" s="8">
-        <v>0.014105241463305522</v>
+        <v>0.014105241463306422</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,13 +907,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7">
-        <v>14.07056156133968</v>
+        <v>14.070561561339684</v>
       </c>
       <c r="C24" s="7">
-        <v>13.89434116454233</v>
+        <v>13.894341164542322</v>
       </c>
       <c r="D24" s="8">
-        <v>0.012682889725426865</v>
+        <v>0.01268288972542777</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1066,7 +1066,7 @@
         <v>46306</v>
       </c>
       <c r="R2" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S2" s="12" t="s">
         <v>39</v>
@@ -1121,7 +1121,7 @@
         <v>46306</v>
       </c>
       <c r="R3" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>39</v>
@@ -1176,7 +1176,7 @@
         <v>46306</v>
       </c>
       <c r="R4" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S4" s="12" t="s">
         <v>39</v>
@@ -1231,7 +1231,7 @@
         <v>46306</v>
       </c>
       <c r="R5" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>39</v>
@@ -1270,7 +1270,7 @@
         <v>46306</v>
       </c>
       <c r="R6" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>39</v>
@@ -1309,7 +1309,7 @@
         <v>46306</v>
       </c>
       <c r="R7" s="4">
-        <v>46306.656111840275</v>
+        <v>46306.92434909722</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>39</v>
@@ -1354,7 +1354,7 @@
         <v>46277</v>
       </c>
       <c r="B2" s="7">
-        <v>419.66999999999996</v>
+        <v>419.67</v>
       </c>
       <c r="C2" s="9">
         <v>29433</v>
@@ -1371,7 +1371,7 @@
         <v>46278</v>
       </c>
       <c r="B3" s="7">
-        <v>456.79</v>
+        <v>456.78999999999996</v>
       </c>
       <c r="C3" s="9">
         <v>31758</v>
@@ -1456,7 +1456,7 @@
         <v>46283</v>
       </c>
       <c r="B8" s="7">
-        <v>436.23</v>
+        <v>436.22999999999996</v>
       </c>
       <c r="C8" s="9">
         <v>30139</v>
@@ -1473,7 +1473,7 @@
         <v>46284</v>
       </c>
       <c r="B9" s="7">
-        <v>366.94000000000005</v>
+        <v>366.94</v>
       </c>
       <c r="C9" s="9">
         <v>25222</v>
@@ -1490,7 +1490,7 @@
         <v>46285</v>
       </c>
       <c r="B10" s="7">
-        <v>428.45000000000005</v>
+        <v>428.45</v>
       </c>
       <c r="C10" s="9">
         <v>29750</v>
@@ -1507,7 +1507,7 @@
         <v>46286</v>
       </c>
       <c r="B11" s="7">
-        <v>417.24</v>
+        <v>417.23999999999995</v>
       </c>
       <c r="C11" s="9">
         <v>29817</v>
@@ -1558,7 +1558,7 @@
         <v>46289</v>
       </c>
       <c r="B14" s="7">
-        <v>413.27</v>
+        <v>413.27000000000004</v>
       </c>
       <c r="C14" s="9">
         <v>29504</v>
@@ -1575,7 +1575,7 @@
         <v>46290</v>
       </c>
       <c r="B15" s="7">
-        <v>452.16</v>
+        <v>452.15999999999997</v>
       </c>
       <c r="C15" s="9">
         <v>31515</v>
@@ -1592,7 +1592,7 @@
         <v>46291</v>
       </c>
       <c r="B16" s="7">
-        <v>479.17999999999995</v>
+        <v>479.18000000000006</v>
       </c>
       <c r="C16" s="9">
         <v>35008</v>
@@ -1626,7 +1626,7 @@
         <v>46293</v>
       </c>
       <c r="B18" s="7">
-        <v>448.43</v>
+        <v>448.42999999999995</v>
       </c>
       <c r="C18" s="9">
         <v>31119</v>
@@ -1728,7 +1728,7 @@
         <v>46299</v>
       </c>
       <c r="B24" s="7">
-        <v>402.28999999999996</v>
+        <v>402.29</v>
       </c>
       <c r="C24" s="9">
         <v>28262</v>
@@ -1813,7 +1813,7 @@
         <v>46304</v>
       </c>
       <c r="B29" s="7">
-        <v>435.97999999999996</v>
+        <v>435.98</v>
       </c>
       <c r="C29" s="9">
         <v>30656</v>
@@ -1830,7 +1830,7 @@
         <v>46305</v>
       </c>
       <c r="B30" s="7">
-        <v>436.49</v>
+        <v>436.48999999999995</v>
       </c>
       <c r="C30" s="9">
         <v>30474</v>

--- a/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
+++ b/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
@@ -779,7 +779,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <v>46306.92436550926</v>
+        <v>46306.940419652776</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -787,7 +787,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1066,7 +1066,7 @@
         <v>46306</v>
       </c>
       <c r="R2" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S2" s="12" t="s">
         <v>39</v>
@@ -1121,7 +1121,7 @@
         <v>46306</v>
       </c>
       <c r="R3" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>39</v>
@@ -1176,7 +1176,7 @@
         <v>46306</v>
       </c>
       <c r="R4" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S4" s="12" t="s">
         <v>39</v>
@@ -1231,7 +1231,7 @@
         <v>46306</v>
       </c>
       <c r="R5" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>39</v>
@@ -1270,7 +1270,7 @@
         <v>46306</v>
       </c>
       <c r="R6" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>39</v>
@@ -1309,7 +1309,7 @@
         <v>46306</v>
       </c>
       <c r="R7" s="4">
-        <v>46306.92434909722</v>
+        <v>46306.940401527776</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>39</v>
@@ -1371,7 +1371,7 @@
         <v>46278</v>
       </c>
       <c r="B3" s="7">
-        <v>456.78999999999996</v>
+        <v>456.79</v>
       </c>
       <c r="C3" s="9">
         <v>31758</v>
@@ -1422,7 +1422,7 @@
         <v>46281</v>
       </c>
       <c r="B6" s="7">
-        <v>462.11</v>
+        <v>462.11000000000007</v>
       </c>
       <c r="C6" s="9">
         <v>32714</v>
@@ -1490,7 +1490,7 @@
         <v>46285</v>
       </c>
       <c r="B10" s="7">
-        <v>428.45</v>
+        <v>428.45000000000005</v>
       </c>
       <c r="C10" s="9">
         <v>29750</v>
@@ -1507,7 +1507,7 @@
         <v>46286</v>
       </c>
       <c r="B11" s="7">
-        <v>417.23999999999995</v>
+        <v>417.24</v>
       </c>
       <c r="C11" s="9">
         <v>29817</v>
@@ -1524,7 +1524,7 @@
         <v>46287</v>
       </c>
       <c r="B12" s="7">
-        <v>418.36</v>
+        <v>418.36000000000007</v>
       </c>
       <c r="C12" s="9">
         <v>30797</v>
@@ -1575,7 +1575,7 @@
         <v>46290</v>
       </c>
       <c r="B15" s="7">
-        <v>452.15999999999997</v>
+        <v>452.16</v>
       </c>
       <c r="C15" s="9">
         <v>31515</v>
@@ -1643,7 +1643,7 @@
         <v>46294</v>
       </c>
       <c r="B19" s="7">
-        <v>413.71</v>
+        <v>413.71000000000004</v>
       </c>
       <c r="C19" s="9">
         <v>29413</v>
@@ -1694,7 +1694,7 @@
         <v>46297</v>
       </c>
       <c r="B22" s="7">
-        <v>416.64</v>
+        <v>416.64000000000004</v>
       </c>
       <c r="C22" s="9">
         <v>27944</v>

--- a/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
+++ b/docs/logo-relatorio/amostras/relatorio-com-logo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>AdsPilot — Resumo executivo</t>
   </si>
@@ -89,6 +89,21 @@
   </si>
   <si>
     <t>ROAS</t>
+  </si>
+  <si>
+    <t>Leads</t>
+  </si>
+  <si>
+    <t>CPL (custo por lead)</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>CPA (custo por compra)</t>
+  </si>
+  <si>
+    <t>Taxa de conversão (resultados ÷ cliques)</t>
   </si>
   <si>
     <t>Campanha</t>
@@ -721,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -779,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <v>46306.940419652776</v>
+        <v>46306.95802251158</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -787,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -809,13 +824,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7">
-        <v>12759.34</v>
+        <v>12759.339999999997</v>
       </c>
       <c r="C17" s="7">
-        <v>12785.669999999996</v>
+        <v>12785.670000000004</v>
       </c>
       <c r="D17" s="8">
-        <v>-0.0020593367418364696</v>
+        <v>-0.002059336741837322</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -865,13 +880,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>6.635122204888195</v>
+        <v>6.6351222048881935</v>
       </c>
       <c r="C21" s="7">
-        <v>6.73994201370585</v>
+        <v>6.739942013705853</v>
       </c>
       <c r="D21" s="8">
-        <v>-0.01555203421698596</v>
+        <v>-0.015552034216986744</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -893,13 +908,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>0.7570511451287528</v>
+        <v>0.7570511451287526</v>
       </c>
       <c r="C23" s="7">
-        <v>0.7465212821860219</v>
+        <v>0.7465212821860223</v>
       </c>
       <c r="D23" s="8">
-        <v>0.014105241463306422</v>
+        <v>0.014105241463305522</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,13 +922,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7">
-        <v>14.070561561339684</v>
+        <v>14.07056156133968</v>
       </c>
       <c r="C24" s="7">
-        <v>13.894341164542322</v>
+        <v>13.89434116454233</v>
       </c>
       <c r="D24" s="8">
-        <v>0.01268288972542777</v>
+        <v>0.012682889725426865</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -928,6 +943,76 @@
       </c>
       <c r="D25" s="8">
         <v>-5.068916758014455e-7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9">
+        <v>310</v>
+      </c>
+      <c r="C26" s="9">
+        <v>312</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-0.00641025641025641</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7">
+        <v>18.571999999999996</v>
+      </c>
+      <c r="C27" s="7">
+        <v>18.554102564102557</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0.0009646080070757828</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9">
+        <v>366</v>
+      </c>
+      <c r="C28" s="9">
+        <v>369</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-0.008130081300813009</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7">
+        <v>15.387295081967215</v>
+      </c>
+      <c r="C29" s="7">
+        <v>15.341300813008132</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0.002998068385445099</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10">
+        <v>0.11409754360982555</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0.1107607870613651</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0.030125793044534624</v>
       </c>
     </row>
   </sheetData>
@@ -958,7 +1043,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>6</v>
@@ -967,13 +1052,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>17</v>
@@ -988,7 +1073,7 @@
         <v>20</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L1" s="16" t="s">
         <v>22</v>
@@ -1000,34 +1085,34 @@
         <v>24</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>11</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F2" s="7">
         <v>5631.750000000001</v>
@@ -1057,7 +1142,7 @@
         <v>4.199998224352998</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P2" s="13">
         <v>46277</v>
@@ -1066,25 +1151,25 @@
         <v>46306</v>
       </c>
       <c r="R2" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>35</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F3" s="7">
         <v>3414.4700000000003</v>
@@ -1112,7 +1197,7 @@
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P3" s="13">
         <v>46277</v>
@@ -1121,25 +1206,25 @@
         <v>46306</v>
       </c>
       <c r="R3" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F4" s="7">
         <v>2342.8500000000004</v>
@@ -1167,7 +1252,7 @@
       </c>
       <c r="N4" s="11"/>
       <c r="O4" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P4" s="13">
         <v>46277</v>
@@ -1176,25 +1261,25 @@
         <v>46306</v>
       </c>
       <c r="R4" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" s="7">
         <v>1370.27</v>
@@ -1222,7 +1307,7 @@
       </c>
       <c r="N5" s="11"/>
       <c r="O5" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P5" s="13">
         <v>46277</v>
@@ -1231,25 +1316,25 @@
         <v>46306</v>
       </c>
       <c r="R5" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="9"/>
@@ -1261,7 +1346,7 @@
       <c r="M6" s="7"/>
       <c r="N6" s="11"/>
       <c r="O6" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P6" s="13">
         <v>46277</v>
@@ -1270,25 +1355,25 @@
         <v>46306</v>
       </c>
       <c r="R6" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="9"/>
@@ -1300,7 +1385,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="11"/>
       <c r="O7" s="12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P7" s="13">
         <v>46277</v>
@@ -1309,10 +1394,10 @@
         <v>46306</v>
       </c>
       <c r="R7" s="4">
-        <v>46306.940401527776</v>
+        <v>46306.9580050463</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1334,10 +1419,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>17</v>
@@ -1354,7 +1439,7 @@
         <v>46277</v>
       </c>
       <c r="B2" s="7">
-        <v>419.67</v>
+        <v>419.66999999999996</v>
       </c>
       <c r="C2" s="9">
         <v>29433</v>
@@ -1422,7 +1507,7 @@
         <v>46281</v>
       </c>
       <c r="B6" s="7">
-        <v>462.11000000000007</v>
+        <v>462.11</v>
       </c>
       <c r="C6" s="9">
         <v>32714</v>
@@ -1456,7 +1541,7 @@
         <v>46283</v>
       </c>
       <c r="B8" s="7">
-        <v>436.22999999999996</v>
+        <v>436.23</v>
       </c>
       <c r="C8" s="9">
         <v>30139</v>
@@ -1473,7 +1558,7 @@
         <v>46284</v>
       </c>
       <c r="B9" s="7">
-        <v>366.94</v>
+        <v>366.94000000000005</v>
       </c>
       <c r="C9" s="9">
         <v>25222</v>
@@ -1524,7 +1609,7 @@
         <v>46287</v>
       </c>
       <c r="B12" s="7">
-        <v>418.36000000000007</v>
+        <v>418.36</v>
       </c>
       <c r="C12" s="9">
         <v>30797</v>
@@ -1558,7 +1643,7 @@
         <v>46289</v>
       </c>
       <c r="B14" s="7">
-        <v>413.27000000000004</v>
+        <v>413.27</v>
       </c>
       <c r="C14" s="9">
         <v>29504</v>
@@ -1592,7 +1677,7 @@
         <v>46291</v>
       </c>
       <c r="B16" s="7">
-        <v>479.18000000000006</v>
+        <v>479.17999999999995</v>
       </c>
       <c r="C16" s="9">
         <v>35008</v>
@@ -1626,7 +1711,7 @@
         <v>46293</v>
       </c>
       <c r="B18" s="7">
-        <v>448.42999999999995</v>
+        <v>448.43</v>
       </c>
       <c r="C18" s="9">
         <v>31119</v>
@@ -1643,7 +1728,7 @@
         <v>46294</v>
       </c>
       <c r="B19" s="7">
-        <v>413.71000000000004</v>
+        <v>413.71</v>
       </c>
       <c r="C19" s="9">
         <v>29413</v>
@@ -1694,7 +1779,7 @@
         <v>46297</v>
       </c>
       <c r="B22" s="7">
-        <v>416.64000000000004</v>
+        <v>416.64</v>
       </c>
       <c r="C22" s="9">
         <v>27944</v>
@@ -1728,7 +1813,7 @@
         <v>46299</v>
       </c>
       <c r="B24" s="7">
-        <v>402.29</v>
+        <v>402.28999999999996</v>
       </c>
       <c r="C24" s="9">
         <v>28262</v>
@@ -1813,7 +1898,7 @@
         <v>46304</v>
       </c>
       <c r="B29" s="7">
-        <v>435.98</v>
+        <v>435.97999999999996</v>
       </c>
       <c r="C29" s="9">
         <v>30656</v>
@@ -1830,7 +1915,7 @@
         <v>46305</v>
       </c>
       <c r="B30" s="7">
-        <v>436.48999999999995</v>
+        <v>436.49</v>
       </c>
       <c r="C30" s="9">
         <v>30474</v>
@@ -1876,122 +1961,122 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
